--- a/Workflows/Chemical validation/Level0_Templates/XXXX_XX_DOC_TN.xlsx
+++ b/Workflows/Chemical validation/Level0_Templates/XXXX_XX_DOC_TN.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnun365-my.sharepoint.com/personal/jtorrens_unav_es/Documents/Documentos/LICA/data/plantillas/Forest/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtorrens\ICP\repoGitLab\lifewatch-vre\Workflows\Chemical validation\Level0_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{AE7C82AE-8C8D-4882-9E7D-A823FAA85301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88873473-1370-4501-8051-6E5922B48C4A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD85B47-8EA5-41F7-8380-3E09A4CC6925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>SiteName</t>
   </si>
@@ -53,213 +53,6 @@
   </si>
   <si>
     <t>TN(mg/l)</t>
-  </si>
-  <si>
-    <t>05PS INT</t>
-  </si>
-  <si>
-    <t>05PS INT NIEVE</t>
-  </si>
-  <si>
-    <t>05PS INT LIX 20</t>
-  </si>
-  <si>
-    <t>05PS INT LIX 60</t>
-  </si>
-  <si>
-    <t>05PS INT LIX G 20</t>
-  </si>
-  <si>
-    <t>05PS INT LIX G 60</t>
-  </si>
-  <si>
-    <t>05PS EXT</t>
-  </si>
-  <si>
-    <t>05PS EXT NIEVE</t>
-  </si>
-  <si>
-    <t>06QI INT</t>
-  </si>
-  <si>
-    <t>06QI EXT</t>
-  </si>
-  <si>
-    <t>07QI INT</t>
-  </si>
-  <si>
-    <t>07QI EXT</t>
-  </si>
-  <si>
-    <t>10PPA INT</t>
-  </si>
-  <si>
-    <t>10PPA EXT</t>
-  </si>
-  <si>
-    <t>11QS INT</t>
-  </si>
-  <si>
-    <t>11QS EXT</t>
-  </si>
-  <si>
-    <t>22PN INT</t>
-  </si>
-  <si>
-    <t>22PN INT NIEVE</t>
-  </si>
-  <si>
-    <t>22PN EXT</t>
-  </si>
-  <si>
-    <t>22PN EXT NIEVE</t>
-  </si>
-  <si>
-    <t>25PH INT</t>
-  </si>
-  <si>
-    <t>25PH EXT</t>
-  </si>
-  <si>
-    <t>26QI INT</t>
-  </si>
-  <si>
-    <t>26QI EXT</t>
-  </si>
-  <si>
-    <t>30PS INT</t>
-  </si>
-  <si>
-    <t>30PS INT NIEVE</t>
-  </si>
-  <si>
-    <t>30PS INT LIX 20</t>
-  </si>
-  <si>
-    <t>30PS INT LIX 60</t>
-  </si>
-  <si>
-    <t>30PS EXT</t>
-  </si>
-  <si>
-    <t>30PS EXT NIEVE</t>
-  </si>
-  <si>
-    <t>33QPE INT</t>
-  </si>
-  <si>
-    <t>33QPE INT NIEVE</t>
-  </si>
-  <si>
-    <t>33QPE INT LIX 20</t>
-  </si>
-  <si>
-    <t>33QPE INT LIX 60</t>
-  </si>
-  <si>
-    <t>33QPE EXT</t>
-  </si>
-  <si>
-    <t>33QPE EXT NIEVE</t>
-  </si>
-  <si>
-    <t>37PPR INT</t>
-  </si>
-  <si>
-    <t>37PPR EXT</t>
-  </si>
-  <si>
-    <t>54PH INT</t>
-  </si>
-  <si>
-    <t>54PH EXT</t>
-  </si>
-  <si>
-    <t>102PPR INT</t>
-  </si>
-  <si>
-    <t>102PPR INT LIX 20</t>
-  </si>
-  <si>
-    <t>102PPR INT LIX 60</t>
-  </si>
-  <si>
-    <t>102PPR EXT</t>
-  </si>
-  <si>
-    <t>115FS INT</t>
-  </si>
-  <si>
-    <t>115FS INT NIEVE</t>
-  </si>
-  <si>
-    <t>115FS INT LIX 20</t>
-  </si>
-  <si>
-    <t>115FS INT LIX 60</t>
-  </si>
-  <si>
-    <t>115FS EXT</t>
-  </si>
-  <si>
-    <t>115FS EXT NIEVE</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Valsain</t>
-  </si>
-  <si>
-    <t>Morella</t>
-  </si>
-  <si>
-    <t>Majadas</t>
-  </si>
-  <si>
-    <t>Almonte</t>
-  </si>
-  <si>
-    <t>Villanueva de la Sierra</t>
-  </si>
-  <si>
-    <t>Mora de Rubielos</t>
-  </si>
-  <si>
-    <t>Tibi</t>
-  </si>
-  <si>
-    <t>Andujar</t>
-  </si>
-  <si>
-    <t>Soria</t>
-  </si>
-  <si>
-    <t>Cervera de Pisuerga</t>
-  </si>
-  <si>
-    <t>Cuellar</t>
-  </si>
-  <si>
-    <t>El Saler</t>
-  </si>
-  <si>
-    <t>Padron</t>
-  </si>
-  <si>
-    <t>Burguete</t>
   </si>
   <si>
     <t>Comments</t>
@@ -379,13 +172,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -400,8 +193,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="95250" y="76200"/>
-          <a:ext cx="12011025" cy="5943600"/>
+          <a:off x="95250" y="76199"/>
+          <a:ext cx="12011025" cy="14992351"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -439,156 +232,1641 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="sng"/>
-            <a:t>PLANTILLA DOC TN</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="sng"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>Esto es la plantilla (XXXX_XX_ES02_DOC_TN.xlsx) para rellenar los datos de DOC y TN en la hoja data. Para cada año y mes se debe rellenar la plantilla una vez. Es IMPORTANTE nombrar la plantilla con el año y mes que corresponde, cambiando las XXXX_XX por el año y mes en cuestión (ej: 2023_06_ES02_DOC_TN.xlsx). La idea es copiar en esta plantilla los datos que se han logrado en el laboratorio. No es necesario eliminar ninguna fila, y si falta un dato o se ha</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none" baseline="0"/>
-            <a:t> obtenido un dato erróneo, no añadirlo y dejar la celda vacía.</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-ES" sz="1400" u="none"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="none"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>Columnas:</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="none"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>TEMPLATE: XXXX_XX_DOC_TN.xlsx</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>PURPOSE</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>This template records dissolved organic carbon (DOC) and total nitrogen (TN) concentrations in water samples. One row per analytical sample.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>FILE NAMING CONVENTION</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>YYYY_MM_DOC_TN.xlsx     — original analysis</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>YYYY_MM_DOC_TN_REP.xlsx — repeated analysis</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Where YYYY = year, MM = month of collection. If differente years or months are collected in the same template, you could</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>keep XX.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>COLUMNS</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>SampleID</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="0" u="none"/>
-            <a:t>: identificador único para los diferentes puntos de muestreo de las parcelas de estudio en la región de muestreo. Cada parcela corresponde a un subprograma de ICPIM.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Unique identifier for the analytical sample. This is the key that links this template to all other templates and to the samplesInfo.xlsx metadata file.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use the standardised ICP sample code for the plot and subprogramme. The code combines the plot number, the species abbreviation, the collection type (INT = interior/throughfall, EXT = exterior/bulk deposition) and any additional qualifier: INT         = throughfall (interior of the forest) EXT         = bulk open-field deposition (exterior) NIEVE       = snow sample LIX 20      = soil lysimeter at 20 cm depth LIX 60      = soil lysimeter at 60 cm depth LIX G 20    = gravity lysimeter at 20 cm depth LIX G 60    = gravity lysimeter at 60 cm depth</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>05PS INT, 22PN EXT NIEVE, 30PS INT LIX 20, 115FS EXT</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty. Must be identical across all templates for the same sample in the same month.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>SiteCode</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Numeric code identifying the monitoring plot.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use the official ICP plot number (e.g. 05, 22, 115). Do not include leading zeros beyond the standard format.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>05, 06, 22, 102, 115</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>SiteName</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>: nombre de donde se encuentran las muestras de trabajo.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>PlotCode</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>: codigo de la zona donde se encuentran las muestras de trabajo.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>ScodeICPIM</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>: codigo del tipo de parcela. Este codigo tambien corresponde al subprograma, ya que cada tipo de parcela corresponde a un subpograma de ICPIM diferente.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Name of the monitoring plot or location.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Use the official name of the plot (e.g. Valsain, Bertiz).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Valsain, Mora de Rubielos, Burguete</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>StartDate</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Date on which sample collection began (start of the accumulation period for the collector).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Format DD/MM/YYYY. Leave empty if not recorded.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>01/01/2025, 15/03/2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>EndDate</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>: fecha del día en el que se ha recogido la muestra. Formato: dd/mm/YYYY</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>DOC(mg/l): </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>DOC calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" b="1" u="none"/>
-            <a:t>TN(mg/l):</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t> TN calculado para la muestra. Es importante poner los decimales con comas (ej: 0,03).</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="none"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>En este caso se realiza una plantillla para cada mes del año, 12 plantillas diferentes.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="none"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>MUCHAS GRACIAS POR EL ESFUERZO Y COLABORACIÓN!!</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1400" u="none"/>
-            <a:t>CUALQUIER DUDA NO DUDEIS EN PREGUNTARME (jtorrens@unav.es)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="sng"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="sng"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="sng"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="sng"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" u="sng"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" b="0" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" b="1" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400" baseline="0"/>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="es-ES" sz="1400"/>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Date on which sample collection ended (date the collector was retrieved and the sample taken to the lab).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Format DD/MM/YYYY.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>31/01/2025, 28/02/2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>year</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Year of collection (integer).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Four-digit year. Must match the YYYY in the filename.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2024, 2025</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>month</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Month of collection (integer, 1–12).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Numeric month without leading zero.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1, 6, 12</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Must not be empty.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>DOC(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Dissolved organic carbon concentration in mg/L. DOC is a key indicator of organic matter inputs from the canopy and soil. It is also used in the workflow to estimate the organic anion charge (Org-) for the ion balance calculation.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Enter the value from the laboratory report.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4.27, 1.50, 8.00</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>TN(mg/l)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Total nitrogen concentration in mg/L (sum of all nitrogen</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>forms</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>NO3-N, NH4-N, and dissolved organic nitrogen).</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Enter the value from the laboratory report. TN must always be greater than or equal to NO3-N + NH4-N — if TN is lower, the sample will be flagged in the chemical validation step.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Examples: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>0.29, 0.50, 1.20</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional. Cannot be negative.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" u="sng">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Comments</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES" sz="1100" b="1" u="sng">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- What it is: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Free-text field for any relevant observation about this sample.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- How to fill: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Note any anomalies, collection issues, or observations that may affect data interpretation (e.g. "collector contaminated", "sample collected one week late", "snow sample mixed with rain"). Leave empty if nothing to report.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>- Rules: </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Optional.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-ES">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -894,7 +2172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1DD1C9D-C8E5-4B60-A994-86B75D81D72C}">
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="11.42578125" style="1"/>
@@ -1508,9 +2786,1187 @@
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
     </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
+      <c r="Q43" s="6"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="6"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="6"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="6"/>
+      <c r="Q49" s="6"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+      <c r="P50" s="6"/>
+      <c r="Q50" s="6"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="6"/>
+      <c r="Q51" s="6"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="6"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="P53" s="6"/>
+      <c r="Q53" s="6"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="6"/>
+      <c r="P54" s="6"/>
+      <c r="Q54" s="6"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="6"/>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="6"/>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="6"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="6"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="6"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="6"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="6"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="6"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="6"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
+      <c r="P68" s="6"/>
+      <c r="Q68" s="6"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
+      <c r="O69" s="6"/>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="6"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="6"/>
+      <c r="Q70" s="6"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="6"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="6"/>
+      <c r="P72" s="6"/>
+      <c r="Q72" s="6"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="6"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
+      <c r="P74" s="6"/>
+      <c r="Q74" s="6"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6"/>
+      <c r="P75" s="6"/>
+      <c r="Q75" s="6"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="6"/>
+      <c r="P76" s="6"/>
+      <c r="Q76" s="6"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="6"/>
+      <c r="O77" s="6"/>
+      <c r="P77" s="6"/>
+      <c r="Q77" s="6"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
+      <c r="P78" s="6"/>
+      <c r="Q78" s="6"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="6"/>
+      <c r="P79" s="6"/>
+      <c r="Q79" s="6"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="6"/>
+      <c r="P80" s="6"/>
+      <c r="Q80" s="6"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="6"/>
+      <c r="O81" s="6"/>
+      <c r="P81" s="6"/>
+      <c r="Q81" s="6"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="6"/>
+      <c r="O82" s="6"/>
+      <c r="P82" s="6"/>
+      <c r="Q82" s="6"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="6"/>
+      <c r="O83" s="6"/>
+      <c r="P83" s="6"/>
+      <c r="Q83" s="6"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="6"/>
+      <c r="O84" s="6"/>
+      <c r="P84" s="6"/>
+      <c r="Q84" s="6"/>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="6"/>
+      <c r="O85" s="6"/>
+      <c r="P85" s="6"/>
+      <c r="Q85" s="6"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="6"/>
+      <c r="P86" s="6"/>
+      <c r="Q86" s="6"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="6"/>
+      <c r="P87" s="6"/>
+      <c r="Q87" s="6"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="6"/>
+      <c r="P88" s="6"/>
+      <c r="Q88" s="6"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="6"/>
+      <c r="N89" s="6"/>
+      <c r="O89" s="6"/>
+      <c r="P89" s="6"/>
+      <c r="Q89" s="6"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="6"/>
+      <c r="P90" s="6"/>
+      <c r="Q90" s="6"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="6"/>
+      <c r="P91" s="6"/>
+      <c r="Q91" s="6"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="6"/>
+      <c r="P92" s="6"/>
+      <c r="Q92" s="6"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="6"/>
+      <c r="P93" s="6"/>
+      <c r="Q93" s="6"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
+      <c r="P94" s="6"/>
+      <c r="Q94" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q32"/>
+    <mergeCell ref="A1:Q94"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1540,22 +3996,22 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>3</v>
@@ -1564,19 +4020,13 @@
         <v>4</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>60</v>
-      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -1586,15 +4036,9 @@
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -1604,15 +4048,9 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1622,15 +4060,9 @@
       <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
@@ -1640,15 +4072,9 @@
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -1658,15 +4084,9 @@
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -1676,15 +4096,9 @@
       <c r="J7" s="4"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -1694,15 +4108,9 @@
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>60</v>
-      </c>
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -1712,15 +4120,9 @@
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1730,15 +4132,9 @@
       <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>61</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1748,15 +4144,9 @@
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1766,15 +4156,9 @@
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>62</v>
-      </c>
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1784,15 +4168,9 @@
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -1802,15 +4180,9 @@
       <c r="J14" s="4"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>63</v>
-      </c>
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -1820,15 +4192,9 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -1838,15 +4204,9 @@
       <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -1856,15 +4216,9 @@
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="5">
-        <v>22</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -1874,15 +4228,9 @@
       <c r="J18" s="4"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="5">
-        <v>22</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -1892,15 +4240,9 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="5">
-        <v>22</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -1910,15 +4252,9 @@
       <c r="J20" s="4"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="5">
-        <v>22</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -1928,15 +4264,9 @@
       <c r="J21" s="4"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="5">
-        <v>25</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -1946,15 +4276,9 @@
       <c r="J22" s="4"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="5">
-        <v>25</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>66</v>
-      </c>
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -1964,15 +4288,9 @@
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="5">
-        <v>26</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>67</v>
-      </c>
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -1982,15 +4300,9 @@
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="5">
-        <v>26</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>67</v>
-      </c>
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -2000,15 +4312,9 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="5">
-        <v>30</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -2018,15 +4324,9 @@
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="5">
-        <v>30</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="A27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -2036,15 +4336,9 @@
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="5">
-        <v>30</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -2054,15 +4348,9 @@
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="5">
-        <v>30</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -2072,15 +4360,9 @@
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="5">
-        <v>30</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -2090,15 +4372,9 @@
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="5">
-        <v>30</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>68</v>
-      </c>
+      <c r="A31" s="4"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -2108,15 +4384,9 @@
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="5">
-        <v>33</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
@@ -2126,15 +4396,9 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" s="5">
-        <v>33</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -2144,15 +4408,9 @@
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5">
-        <v>33</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -2162,15 +4420,9 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5">
-        <v>33</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -2180,15 +4432,9 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5">
-        <v>33</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -2198,15 +4444,9 @@
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5">
-        <v>33</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -2216,15 +4456,9 @@
       <c r="J37" s="4"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5">
-        <v>37</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -2234,15 +4468,9 @@
       <c r="J38" s="4"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5">
-        <v>37</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -2252,15 +4480,9 @@
       <c r="J39" s="4"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5">
-        <v>54</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>71</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -2270,15 +4492,9 @@
       <c r="J40" s="4"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5">
-        <v>54</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>71</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -2288,15 +4504,9 @@
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5">
-        <v>102</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -2306,15 +4516,9 @@
       <c r="J42" s="4"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" s="5">
-        <v>102</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -2324,15 +4528,9 @@
       <c r="J43" s="4"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B44" s="5">
-        <v>102</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -2342,15 +4540,9 @@
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B45" s="5">
-        <v>102</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>72</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -2360,15 +4552,9 @@
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" s="5">
-        <v>115</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -2378,15 +4564,9 @@
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="5">
-        <v>115</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -2396,15 +4576,9 @@
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="5">
-        <v>115</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -2414,15 +4588,9 @@
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B49" s="5">
-        <v>115</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -2432,15 +4600,9 @@
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B50" s="5">
-        <v>115</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
@@ -2450,15 +4612,9 @@
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="5">
-        <v>115</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>73</v>
-      </c>
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>

--- a/Workflows/Chemical validation/Level0_Templates/XXXX_XX_DOC_TN.xlsx
+++ b/Workflows/Chemical validation/Level0_Templates/XXXX_XX_DOC_TN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtorrens\ICP\repoGitLab\lifewatch-vre\Workflows\Chemical validation\Level0_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD85B47-8EA5-41F7-8380-3E09A4CC6925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{452CFF65-D215-47CC-97A7-9838952FF4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3FD923B0-A352-4B39-804E-C5D1C21F4722}"/>
   </bookViews>
@@ -545,7 +545,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Use the standardised ICP sample code for the plot and subprogramme. The code combines the plot number, the species abbreviation, the collection type (INT = interior/throughfall, EXT = exterior/bulk deposition) and any additional qualifier: INT         = throughfall (interior of the forest) EXT         = bulk open-field deposition (exterior) NIEVE       = snow sample LIX 20      = soil lysimeter at 20 cm depth LIX 60      = soil lysimeter at 60 cm depth LIX G 20    = gravity lysimeter at 20 cm depth LIX G 60    = gravity lysimeter at 60 cm depth</a:t>
+            <a:t>Use the standardised ICP sample code for the plot and subprogramme. The code could combines the plot number, the species abbreviation, the collection type (INT = interior/throughfall, EXT = exterior/bulk deposition) and any additional qualifier: INT         = throughfall (interior of the forest) EXT         = bulk open-field deposition (exterior) NIEVE       = snow sample LIX 20      = soil lysimeter at 20 cm depth LIX 60      = soil lysimeter at 60 cm depth LIX G 20    = gravity lysimeter at 20 cm depth LIX G 60    = gravity lysimeter at 60 cm depth</a:t>
           </a:r>
           <a:endParaRPr lang="es-ES">
             <a:effectLst/>
@@ -669,6 +669,18 @@
             <a:t>- How to fill: </a:t>
           </a:r>
           <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>You could use </a:t>
+          </a:r>
+          <a:r>
             <a:rPr lang="en-US" sz="1100">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
@@ -678,7 +690,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Use the official ICP plot number (e.g. 05, 22, 115). Do not include leading zeros beyond the standard format.</a:t>
+            <a:t>the official ICP plot number (e.g. 05, 22, 115). Do not include leading zeros beyond the standard format.</a:t>
           </a:r>
           <a:endParaRPr lang="es-ES">
             <a:effectLst/>
